--- a/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python 驱动测试设计及用例.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python 驱动测试设计及用例.xlsx
@@ -13,6 +13,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">接口分析!$E$1:$E$128</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -2184,10 +2187,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网络异常、节点异常(放到后面)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>get_datacenter下的各接口，</t>
     </r>
@@ -2218,6 +2217,10 @@
   </si>
   <si>
     <t xml:space="preserve">     3.python驱动的异常处理？？？---跟许导确认是否需要统一修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络异常、节点异常(通过异常类覆盖测试，放到后面)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2660,7 +2663,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="27">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2725,12 +2728,12 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -3063,30 +3066,30 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="27">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="15" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="27">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6" t="s">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="15" t="s">
         <v>434</v>
       </c>
     </row>
@@ -3115,26 +3118,26 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="27">
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="15" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15" t="s">
         <v>153</v>
       </c>
     </row>
@@ -3181,56 +3184,56 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="27">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6" t="s">
+      <c r="D39" s="14"/>
+      <c r="E39" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="F39" s="6"/>
+      <c r="F39" s="15"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="6"/>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="F40" s="6"/>
+      <c r="F40" s="15"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="6"/>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6" t="s">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="6"/>
-      <c r="B42" s="5" t="s">
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="1:6" ht="27">
+      <c r="A42" s="15"/>
+      <c r="B42" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="F42" s="6"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F42" s="15"/>
     </row>
     <row r="43" spans="1:6" ht="27">
       <c r="A43" s="16" t="s">
@@ -3241,7 +3244,7 @@
       <c r="D43" s="17"/>
       <c r="E43" s="16"/>
       <c r="F43" s="16" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="27">
@@ -3261,7 +3264,7 @@
         <v>417</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="27">
@@ -5321,6 +5324,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="E1:E128"/>
   <mergeCells count="1">
     <mergeCell ref="G93:G106"/>
   </mergeCells>

--- a/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python 驱动测试设计及用例.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python 驱动测试设计及用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="4" r:id="rId1"/>
